--- a/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 그냥... 제 안에서 뭔가가 꺼져버린 것 같은 느낌이 들어서 왔어요. 그러니까, 퇴근하고 남편이랑 같이 앉아 있거나 제가 보던 드라마를 보려고 해도, 원래는 편안하거나 행복해야 하는 게 맞잖아요... 근데 그냥 그게 안 느껴져요. 마치 아무것도 없는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌이 든 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 3주 정도 됐어요. 직장에서 팔레트가 무너져서 동료가 다친 뒤부터 시작됐어요. 그 이후로 계속 뭔가 제 상태가 정상이 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 직장에서 이 사고가 있기 전에 즐거워하셨던 활동들을 지금도 즐기고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아니요, 별로 그렇지 않아요. 퇴근하고 남편이랑 같이 앉아 있거나 제가 보던 드라마를 틀어놓거든요, 예전에는 그게 편안하고 행복했던 거 같은데... 지금은 그냥 좀 멍해요. 제 안에 따뜻한 부분이 꺼져버린 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이 사고가 일어난 이후로 대부분의 시간 동안 슬픈 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 대부분의 시간 동안 슬프다고 해야 할지는 잘 모르겠어요. 그보다는 좀 멍하고 텅 빈 느낌에 가까워요. 딱히 울거나 그러진 않는데... 그냥 제가 제 같지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이 사고 이후로 여전히 즐겁게 하시거나 즐거움을 느끼는 활동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 퇴근 후에 남편이랑 같이 앉아 있거나 드라마를 보려고는 하는데, 거기서 딱히 얻어지는 게 없어요. 예전에는 그런 게 위안이 되고 어쩌면 조금 행복하게 만들어줬던 것 같은데, 지금은 그냥 아무것도 없는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 예전에 즐기셨던 것들에 대한 흥미를 잃으셨다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네... 그런 것 같아요. 여전히 똑같은 걸 해요, 퇴근하고 남편이랑 앉아 있거나 드라마를 틀어놓는 거요. 근데 예전만큼 좋게 느껴지지가 않아요. 원래는 위안이 되어야 하는데, 그냥 좀 텅 빈 것 같아요, 그 따뜻한 느낌이 사라진 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 대부분의 시간 동안 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 대부분의 시간 동안 슬프다고는 말 못 할 것 같아요. 그냥 좀 멍하고 이상한 느낌에 가까워요. 뭔가 느껴야 하는 건 아는데, 실제로는 딱히 안 느껴지는 거요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 체중이 줄어드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 재보지도 않았고, 옷이 달라졌다는 느낌도 딱히 못 받았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 죽음에 대한 생각이나 차라리 죽었으면 하는 생각이 드신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 그건... 아닌 것 같아요. 죽고 싶다거나 그런 생각은 안 했어요. 그냥 좀 멍한 느낌이지, 저 자신을 해치고 싶은 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 예전보다 기운이 덜하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나 그렇듯 피곤하긴 한데, 예전보다 기운이 확 줄었다는 걸 뚜렷하게 느낀 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 혼자 계실 때 대부분 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 혼자 있을 때 대부분 슬프다고는 말 못 할 것 같아요. 가끔 그냥 좀 멍하거나 이상한 느낌이 드는데, 그런 식으로 딱히 챙겨보진 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 예전보다 더 피곤하다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네... 그런 것 같아요, 주로 잠을 제대로 못 자서 그런 거 같아요. 야간 근무 끝나면 완전히 지치는데, 막 잠들려고 하면 팔레트가 무너지는 소리를 들은 것처럼 흠칫 놀라서 깨요. 잠을 자도, 일어나면 제대로 쉰 것 같지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 식욕에 변화가 있다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 큰 변화는 딱히 못 느꼈어요. 그러니까, 여전히 먹긴 먹어요, 어떤 날은 그거에 대해 별로 생각을 안 하기도 하는데, 식욕이 뚜렷하게 달라졌다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 대부분의 시간 동안 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 대부분의 시간 동안은 아니에요. 가끔 기분이 처지거나 제가 아닌 것 같은 순간들이 있긴 한데, 하루 종일 혹은 대부분 슬프다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 하루 중 대부분 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 하루 대부분은 아닌 것 같아요. 가끔 속상하긴 한데, 하루 종일 슬픈 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 그러니까, 가끔은 슬프긴 해요, 네. 근데 왔다 갔다 하는 것 같아요. 항상 슬픈 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네, 가끔은 그래요. 그거 말고는 더 뭐라고 말씀드려야 할지 잘 모르겠어요. 계속 그런 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 그건 제가 할 수 있는 만큼 최대한 답변드린 것 같아요. 네, 가끔 슬프긴 한데, 더 덧붙일 말은 별로 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 이 슬픔이 가벼운 정도라고 느끼시나요, 아니면 일상생활에 상당한 지장을 주고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 지장을 주고 있어요, 네. 지금은 평소 하던 입고 업무를 제대로 못 하고 있어요. 팔레트 옮기다가 얼어붙어 버렸고, 그러고 나서 누군가에게 화를 냈어요. 안전하게 일하지 못한다는 이유로 상사가 저를 현장 업무에서 빼야 했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 슬픔의 정도를 가볍다고 표현하시겠어요, 아니면 심하다고 표현하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 심하다기보다는 중간 정도라고 해야 할 것 같아요. 매 순간 짓누르는 정도는 아니지만, 확실히 저한테 영향을 주고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 급성 스트레스장애 (D019)
 인구통계: 성별 여성 / 나이 36 / 직업상태 stocker or order filler / 최종학력 고등학교 졸업
@@ -575,488 +999,35 @@
 증상 지속 기간: 3 weeks
 추가 요건: 
 주호소 증상 코드: S076
-배경 서술: 아만다가 일하는 창고가 신규 지역 유통 계약을 처리하기 위해 심야 하역 일정으로 전환되면서, 그녀는 평소보다 더 높은 임시 선반과 더 무거운 팔레트를 다뤄야 하는, 인력이 부족한 입고팀에 배치되었다. 어느 근무 중, 그녀가 있던 통로 근처에서 쌓아 올린 팔레트가 무너지면서 그녀가 직접 교육했던 동료가 심각한 부상을 입었고, 아만다는 그 광경과 더불어 자신이 늘 조심스럽게 지켜온 절차만으로는 그 구역의 안전을 지키기에 충분하지 않았다는 느낌에 큰 충격을 받았다. 이후 3주 동안 그 사건은 수면 장애, 원치 않는 기억, 붕괴 직후 순간들에 대한 기억의 공백, 남편과 평소 취미에 대한 애정 상실, 동료들에 대한 날카로운 분노, 그리고 창고 안 위험을 끊임없이 살피는 모습으로 그녀를 집에서도 직장에서도 따라다녔다. 계절직 직원에게 화를 낸 뒤 일상적인 팔레트 이동 작업 중 얼어붙어 버린 일이 있은 후, 상사는 그녀를 현장 업무에서 빼냈고 아만다는 회사의 근로자 지원 프로그램을 통해 정신건강 평가를 받는 데 동의했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 그냥... 제 안에서 뭔가가 꺼져버린 것 같은 느낌이 들어서 왔어요. 그러니까, 퇴근하고 남편이랑 같이 앉아 있거나 제가 보던 드라마를 보려고 해도, 원래는 편안하거나 행복해야 하는 게 맞잖아요... 근데 그냥 그게 안 느껴져요. 마치 아무것도 없는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌이 든 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 3주 정도 됐어요. 직장에서 팔레트가 무너져서 동료가 다친 뒤부터 시작됐어요. 그 이후로 계속 뭔가 제 상태가 정상이 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 직장에서 이 사고가 있기 전에 즐거워하셨던 활동들을 지금도 즐기고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아니요, 별로 그렇지 않아요. 퇴근하고 남편이랑 같이 앉아 있거나 제가 보던 드라마를 틀어놓거든요, 예전에는 그게 편안하고 행복했던 거 같은데... 지금은 그냥 좀 멍해요. 제 안에 따뜻한 부분이 꺼져버린 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이 사고가 일어난 이후로 대부분의 시간 동안 슬픈 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 대부분의 시간 동안 슬프다고 해야 할지는 잘 모르겠어요. 그보다는 좀 멍하고 텅 빈 느낌에 가까워요. 딱히 울거나 그러진 않는데... 그냥 제가 제 같지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이 사고 이후로 여전히 즐겁게 하시거나 즐거움을 느끼는 활동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 딱히 없어요. 그러니까, 퇴근 후에 남편이랑 같이 앉아 있거나 드라마를 보려고는 하는데, 거기서 딱히 얻어지는 게 없어요. 예전에는 그런 게 위안이 되고 어쩌면 조금 행복하게 만들어줬던 것 같은데, 지금은 그냥 아무것도 없는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 예전에 즐기셨던 것들에 대한 흥미를 잃으셨다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네... 그런 것 같아요. 여전히 똑같은 걸 해요, 퇴근하고 남편이랑 앉아 있거나 드라마를 틀어놓는 거요. 근데 예전만큼 좋게 느껴지지가 않아요. 원래는 위안이 되어야 하는데, 그냥 좀 텅 빈 것 같아요, 그 따뜻한 느낌이 사라진 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 대부분의 시간 동안 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 대부분의 시간 동안 슬프다고는 말 못 할 것 같아요. 그냥 좀 멍하고 이상한 느낌에 가까워요. 뭔가 느껴야 하는 건 아는데, 실제로는 딱히 안 느껴지는 거요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 체중이 줄어드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 잘 모르겠어요. 체중을 재보지도 않았고, 옷이 달라졌다는 느낌도 딱히 못 받았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 죽음에 대한 생각이나 차라리 죽었으면 하는 생각이 드신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 그건... 아닌 것 같아요. 죽고 싶다거나 그런 생각은 안 했어요. 그냥 좀 멍한 느낌이지, 저 자신을 해치고 싶은 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 예전보다 기운이 덜하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 누구나 그렇듯 피곤하긴 한데, 예전보다 기운이 확 줄었다는 걸 뚜렷하게 느낀 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 혼자 계실 때 대부분 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잘 모르겠어요. 혼자 있을 때 대부분 슬프다고는 말 못 할 것 같아요. 가끔 그냥 좀 멍하거나 이상한 느낌이 드는데, 그런 식으로 딱히 챙겨보진 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 예전보다 더 피곤하다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네... 그런 것 같아요, 주로 잠을 제대로 못 자서 그런 거 같아요. 야간 근무 끝나면 완전히 지치는데, 막 잠들려고 하면 팔레트가 무너지는 소리를 들은 것처럼 흠칫 놀라서 깨요. 잠을 자도, 일어나면 제대로 쉰 것 같지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 이런 느낌이 시작된 이후로 식욕에 변화가 있다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 큰 변화는 딱히 못 느꼈어요. 그러니까, 여전히 먹긴 먹어요, 어떤 날은 그거에 대해 별로 생각을 안 하기도 하는데, 식욕이 뚜렷하게 달라졌다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 대부분의 시간 동안 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 대부분의 시간 동안은 아니에요. 가끔 기분이 처지거나 제가 아닌 것 같은 순간들이 있긴 한데, 하루 종일 혹은 대부분 슬프다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 하루 중 대부분 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 하루 대부분은 아닌 것 같아요. 가끔 속상하긴 한데, 하루 종일 슬픈 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 그러니까, 가끔은 슬프긴 해요, 네. 근데 왔다 갔다 하는 것 같아요. 항상 슬픈 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네, 가끔은 그래요. 그거 말고는 더 뭐라고 말씀드려야 할지 잘 모르겠어요. 계속 그런 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 슬프다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 그건 제가 할 수 있는 만큼 최대한 답변드린 것 같아요. 네, 가끔 슬프긴 한데, 더 덧붙일 말은 별로 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 이 슬픔이 가벼운 정도라고 느끼시나요, 아니면 일상생활에 상당한 지장을 주고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 지장을 주고 있어요, 네. 지금은 평소 하던 입고 업무를 제대로 못 하고 있어요. 팔레트 옮기다가 얼어붙어 버렸고, 그러고 나서 누군가에게 화를 냈어요. 안전하게 일하지 못한다는 이유로 상사가 저를 현장 업무에서 빼야 했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 슬픔의 정도를 가볍다고 표현하시겠어요, 아니면 심하다고 표현하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 심하다기보다는 중간 정도라고 해야 할 것 같아요. 매 순간 짓누르는 정도는 아니지만, 확실히 저한테 영향을 주고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 아만다가 일하는 창고가 신규 지역 유통 계약을 처리하기 위해 심야 하역 일정으로 전환되면서, 그녀는 평소보다 더 높은 임시 선반과 더 무거운 팔레트를 다뤄야 하는, 인력이 부족한 입고팀에 배치되었다. 어느 근무 중, 그녀가 있던 통로 근처에서 쌓아 올린 팔레트가 무너지면서 그녀가 직접 교육했던 동료가 심각한 부상을 입었고, 아만다는 그 광경과 더불어 자신이 늘 조심스럽게 지켜온 절차만으로는 그 구역의 안전을 지키기에 충분하지 않았다는 느낌에 큰 충격을 받았다. 이후 3주 동안 그 사건은 수면 장애, 원치 않는 기억, 붕괴 직후 순간들에 대한 기억의 공백, 남편과 평소 취미에 대한 애정 상실, 동료들에 대한 날카로운 분노, 그리고 창고 안 위험을 끊임없이 살피는 모습으로 그녀를 집에서도 직장에서도 따라다녔다. 계절직 직원에게 화를 낸 뒤 일상적인 팔레트 이동 작업 중 얼어붙어 버린 일이 있은 후, 상사는 그녀를 현장 업무에서 빼냈고 아만다는 회사의 근로자 지원 프로그램을 통해 정신건강 평가를 받는 데 동의했다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S071 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S079 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=2, 커버리지=0.3333)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.; 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=2, 커버리지=0.3333)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1023,11 +1028,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.05</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.05</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3816</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
